--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819398</v>
+        <v>119819403</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716516</v>
+        <v>717069</v>
       </c>
       <c r="R6" t="n">
-        <v>7141053</v>
+        <v>7141027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819412</v>
+        <v>119819399</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716959</v>
+        <v>716725</v>
       </c>
       <c r="R7" t="n">
-        <v>7141129</v>
+        <v>7140977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819416</v>
+        <v>119819412</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716940</v>
+        <v>716959</v>
       </c>
       <c r="R8" t="n">
-        <v>7141151</v>
+        <v>7141129</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819408</v>
+        <v>119819407</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716977</v>
+        <v>716980</v>
       </c>
       <c r="R9" t="n">
-        <v>7141124</v>
+        <v>7141022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819399</v>
+        <v>119819409</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716725</v>
+        <v>716976</v>
       </c>
       <c r="R10" t="n">
-        <v>7140977</v>
+        <v>7141127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819406</v>
+        <v>119819410</v>
       </c>
       <c r="B11" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,30 +1700,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717000</v>
+        <v>716975</v>
       </c>
       <c r="R11" t="n">
-        <v>7140997</v>
+        <v>7141125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819415</v>
+        <v>119819402</v>
       </c>
       <c r="B13" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,30 +1922,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716957</v>
+        <v>717018</v>
       </c>
       <c r="R13" t="n">
-        <v>7141116</v>
+        <v>7141012</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819407</v>
+        <v>119819406</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,30 +2033,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716980</v>
+        <v>717000</v>
       </c>
       <c r="R14" t="n">
-        <v>7141022</v>
+        <v>7140997</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819402</v>
+        <v>119819400</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,30 +2144,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717018</v>
+        <v>716743</v>
       </c>
       <c r="R15" t="n">
-        <v>7141012</v>
+        <v>7140981</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819405</v>
+        <v>119819398</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717053</v>
+        <v>716516</v>
       </c>
       <c r="R16" t="n">
-        <v>7141031</v>
+        <v>7141053</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819409</v>
+        <v>119819415</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716976</v>
+        <v>716957</v>
       </c>
       <c r="R17" t="n">
-        <v>7141127</v>
+        <v>7141116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819403</v>
+        <v>119819405</v>
       </c>
       <c r="B18" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,25 +2477,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717069</v>
+        <v>717053</v>
       </c>
       <c r="R18" t="n">
-        <v>7141027</v>
+        <v>7141031</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819410</v>
+        <v>119819408</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716975</v>
+        <v>716977</v>
       </c>
       <c r="R19" t="n">
-        <v>7141125</v>
+        <v>7141124</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819400</v>
+        <v>119819416</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,30 +2699,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716743</v>
+        <v>716940</v>
       </c>
       <c r="R20" t="n">
-        <v>7140981</v>
+        <v>7141151</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819400</v>
+        <v>119819398</v>
       </c>
       <c r="B15" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,30 +2144,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2176,13 +2176,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716743</v>
+        <v>716516</v>
       </c>
       <c r="R15" t="n">
-        <v>7140981</v>
+        <v>7141053</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819398</v>
+        <v>119819400</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,30 +2255,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716516</v>
+        <v>716743</v>
       </c>
       <c r="R16" t="n">
-        <v>7141053</v>
+        <v>7140981</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819415</v>
+        <v>119819405</v>
       </c>
       <c r="B17" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716957</v>
+        <v>717053</v>
       </c>
       <c r="R17" t="n">
-        <v>7141116</v>
+        <v>7141031</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819405</v>
+        <v>119819415</v>
       </c>
       <c r="B18" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,25 +2477,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717053</v>
+        <v>716957</v>
       </c>
       <c r="R18" t="n">
-        <v>7141031</v>
+        <v>7141116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819403</v>
+        <v>119819398</v>
       </c>
       <c r="B6" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717069</v>
+        <v>716516</v>
       </c>
       <c r="R6" t="n">
-        <v>7141027</v>
+        <v>7141053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819399</v>
+        <v>119819413</v>
       </c>
       <c r="B7" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716725</v>
+        <v>716959</v>
       </c>
       <c r="R7" t="n">
-        <v>7140977</v>
+        <v>7141129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819412</v>
+        <v>119819407</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716959</v>
+        <v>716980</v>
       </c>
       <c r="R8" t="n">
-        <v>7141129</v>
+        <v>7141022</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819407</v>
+        <v>119819415</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716980</v>
+        <v>716957</v>
       </c>
       <c r="R9" t="n">
-        <v>7141022</v>
+        <v>7141116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819409</v>
+        <v>119819410</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716976</v>
+        <v>716975</v>
       </c>
       <c r="R10" t="n">
-        <v>7141127</v>
+        <v>7141125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819410</v>
+        <v>119819408</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716975</v>
+        <v>716977</v>
       </c>
       <c r="R11" t="n">
-        <v>7141125</v>
+        <v>7141124</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819401</v>
+        <v>119819406</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,30 +1811,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716978</v>
+        <v>717000</v>
       </c>
       <c r="R12" t="n">
-        <v>7140954</v>
+        <v>7140997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819402</v>
+        <v>119819416</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,30 +1922,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717018</v>
+        <v>716940</v>
       </c>
       <c r="R13" t="n">
-        <v>7141012</v>
+        <v>7141151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819406</v>
+        <v>119819399</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,30 +2033,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717000</v>
+        <v>716725</v>
       </c>
       <c r="R14" t="n">
-        <v>7140997</v>
+        <v>7140977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819398</v>
+        <v>119819409</v>
       </c>
       <c r="B15" t="n">
         <v>91832</v>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716516</v>
+        <v>716976</v>
       </c>
       <c r="R15" t="n">
-        <v>7141053</v>
+        <v>7141127</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819415</v>
+        <v>119819401</v>
       </c>
       <c r="B18" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,25 +2477,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716957</v>
+        <v>716978</v>
       </c>
       <c r="R18" t="n">
-        <v>7141116</v>
+        <v>7140954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819408</v>
+        <v>119819402</v>
       </c>
       <c r="B19" t="n">
         <v>91856</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716977</v>
+        <v>717018</v>
       </c>
       <c r="R19" t="n">
-        <v>7141124</v>
+        <v>7141012</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819416</v>
+        <v>119819403</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,25 +2699,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716940</v>
+        <v>717069</v>
       </c>
       <c r="R20" t="n">
-        <v>7141151</v>
+        <v>7141027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819401</v>
+        <v>119819402</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,30 +2477,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716978</v>
+        <v>717018</v>
       </c>
       <c r="R18" t="n">
-        <v>7140954</v>
+        <v>7141012</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819402</v>
+        <v>119819401</v>
       </c>
       <c r="B19" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2588,30 +2588,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717018</v>
+        <v>716978</v>
       </c>
       <c r="R19" t="n">
-        <v>7141012</v>
+        <v>7140954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819398</v>
+        <v>119819402</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,26 +1149,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716516</v>
+        <v>717018</v>
       </c>
       <c r="R6" t="n">
-        <v>7141053</v>
+        <v>7141012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819413</v>
+        <v>119819416</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716959</v>
+        <v>716940</v>
       </c>
       <c r="R7" t="n">
-        <v>7141129</v>
+        <v>7141151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819407</v>
+        <v>119819399</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716980</v>
+        <v>716725</v>
       </c>
       <c r="R8" t="n">
-        <v>7141022</v>
+        <v>7140977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819415</v>
+        <v>119819412</v>
       </c>
       <c r="B9" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716957</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>7141116</v>
+        <v>7141129</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819410</v>
+        <v>119819405</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716975</v>
+        <v>717053</v>
       </c>
       <c r="R10" t="n">
-        <v>7141125</v>
+        <v>7141031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819408</v>
+        <v>119819400</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,30 +1700,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716977</v>
+        <v>716743</v>
       </c>
       <c r="R11" t="n">
-        <v>7141124</v>
+        <v>7140981</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819406</v>
+        <v>119819403</v>
       </c>
       <c r="B12" t="n">
         <v>89252</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717000</v>
+        <v>717069</v>
       </c>
       <c r="R12" t="n">
-        <v>7140997</v>
+        <v>7141027</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819416</v>
+        <v>119819408</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,25 +1922,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716940</v>
+        <v>716977</v>
       </c>
       <c r="R13" t="n">
-        <v>7141151</v>
+        <v>7141124</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819399</v>
+        <v>119819398</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716725</v>
+        <v>716516</v>
       </c>
       <c r="R14" t="n">
-        <v>7140977</v>
+        <v>7141053</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819409</v>
+        <v>119819415</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716976</v>
+        <v>716957</v>
       </c>
       <c r="R15" t="n">
-        <v>7141127</v>
+        <v>7141116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819400</v>
+        <v>119819407</v>
       </c>
       <c r="B16" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,30 +2255,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716743</v>
+        <v>716980</v>
       </c>
       <c r="R16" t="n">
-        <v>7140981</v>
+        <v>7141022</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819405</v>
+        <v>119819406</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,30 +2366,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717053</v>
+        <v>717000</v>
       </c>
       <c r="R17" t="n">
-        <v>7141031</v>
+        <v>7140997</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819402</v>
+        <v>119819401</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,30 +2477,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717018</v>
+        <v>716978</v>
       </c>
       <c r="R18" t="n">
-        <v>7141012</v>
+        <v>7140954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819401</v>
+        <v>119819409</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2588,25 +2588,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716978</v>
+        <v>716976</v>
       </c>
       <c r="R19" t="n">
-        <v>7140954</v>
+        <v>7141127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819403</v>
+        <v>119819410</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,25 +2699,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717069</v>
+        <v>716975</v>
       </c>
       <c r="R20" t="n">
-        <v>7141027</v>
+        <v>7141125</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819412</v>
+        <v>119819405</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716959</v>
+        <v>717053</v>
       </c>
       <c r="R9" t="n">
-        <v>7141129</v>
+        <v>7141031</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819405</v>
+        <v>119819412</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717053</v>
+        <v>716959</v>
       </c>
       <c r="R10" t="n">
-        <v>7141031</v>
+        <v>7141129</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819405</v>
+        <v>119819412</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717053</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>7141031</v>
+        <v>7141129</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819412</v>
+        <v>119819405</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716959</v>
+        <v>717053</v>
       </c>
       <c r="R10" t="n">
-        <v>7141129</v>
+        <v>7141031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819408</v>
+        <v>119819398</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716977</v>
+        <v>716516</v>
       </c>
       <c r="R13" t="n">
-        <v>7141124</v>
+        <v>7141053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819398</v>
+        <v>119819408</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716516</v>
+        <v>716977</v>
       </c>
       <c r="R14" t="n">
-        <v>7141053</v>
+        <v>7141124</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819398</v>
+        <v>119819408</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716516</v>
+        <v>716977</v>
       </c>
       <c r="R13" t="n">
-        <v>7141053</v>
+        <v>7141124</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819408</v>
+        <v>119819398</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716977</v>
+        <v>716516</v>
       </c>
       <c r="R14" t="n">
-        <v>7141124</v>
+        <v>7141053</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819402</v>
+        <v>119819403</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>89269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,30 +1145,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717018</v>
+        <v>717069</v>
       </c>
       <c r="R6" t="n">
-        <v>7141012</v>
+        <v>7141027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819416</v>
+        <v>119819398</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716940</v>
+        <v>716516</v>
       </c>
       <c r="R7" t="n">
-        <v>7141151</v>
+        <v>7141053</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819399</v>
+        <v>119819410</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716725</v>
+        <v>716975</v>
       </c>
       <c r="R8" t="n">
-        <v>7140977</v>
+        <v>7141125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819412</v>
+        <v>119819416</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716959</v>
+        <v>716940</v>
       </c>
       <c r="R9" t="n">
-        <v>7141129</v>
+        <v>7141151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819405</v>
+        <v>119819407</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,21 +1593,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717053</v>
+        <v>716980</v>
       </c>
       <c r="R10" t="n">
-        <v>7141031</v>
+        <v>7141022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819400</v>
+        <v>119819402</v>
       </c>
       <c r="B11" t="n">
-        <v>89252</v>
+        <v>91874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,30 +1700,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716743</v>
+        <v>717018</v>
       </c>
       <c r="R11" t="n">
-        <v>7140981</v>
+        <v>7141012</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819403</v>
+        <v>119819412</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>91850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,25 +1811,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717069</v>
+        <v>716959</v>
       </c>
       <c r="R12" t="n">
-        <v>7141027</v>
+        <v>7141129</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819408</v>
+        <v>119819406</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>89269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,30 +1922,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716977</v>
+        <v>717000</v>
       </c>
       <c r="R13" t="n">
-        <v>7141124</v>
+        <v>7140997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819398</v>
+        <v>119819408</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>91874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716516</v>
+        <v>716977</v>
       </c>
       <c r="R14" t="n">
-        <v>7141053</v>
+        <v>7141124</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2135,7 @@
         <v>119819415</v>
       </c>
       <c r="B15" t="n">
-        <v>89252</v>
+        <v>89269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819407</v>
+        <v>119819401</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716980</v>
+        <v>716978</v>
       </c>
       <c r="R16" t="n">
-        <v>7141022</v>
+        <v>7140954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819406</v>
+        <v>119819405</v>
       </c>
       <c r="B17" t="n">
-        <v>89252</v>
+        <v>91902</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,30 +2366,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717000</v>
+        <v>717053</v>
       </c>
       <c r="R17" t="n">
-        <v>7140997</v>
+        <v>7141031</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819401</v>
+        <v>119819409</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,25 +2477,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716978</v>
+        <v>716976</v>
       </c>
       <c r="R18" t="n">
-        <v>7140954</v>
+        <v>7141127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819409</v>
+        <v>119819399</v>
       </c>
       <c r="B19" t="n">
-        <v>91832</v>
+        <v>91874</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716976</v>
+        <v>716725</v>
       </c>
       <c r="R19" t="n">
-        <v>7141127</v>
+        <v>7140977</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819410</v>
+        <v>119819400</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>89269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,30 +2699,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716975</v>
+        <v>716743</v>
       </c>
       <c r="R20" t="n">
-        <v>7141125</v>
+        <v>7140981</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819403</v>
+        <v>119819407</v>
       </c>
       <c r="B6" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717069</v>
+        <v>716980</v>
       </c>
       <c r="R6" t="n">
-        <v>7141027</v>
+        <v>7141022</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819398</v>
+        <v>119819403</v>
       </c>
       <c r="B7" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716516</v>
+        <v>717069</v>
       </c>
       <c r="R7" t="n">
-        <v>7141053</v>
+        <v>7141027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819410</v>
+        <v>119819400</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,30 +1367,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716975</v>
+        <v>716743</v>
       </c>
       <c r="R8" t="n">
-        <v>7141125</v>
+        <v>7140981</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819416</v>
+        <v>119819415</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1478,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716940</v>
+        <v>716957</v>
       </c>
       <c r="R9" t="n">
-        <v>7141151</v>
+        <v>7141116</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819407</v>
+        <v>119819406</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,30 +1589,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716980</v>
+        <v>717000</v>
       </c>
       <c r="R10" t="n">
-        <v>7141022</v>
+        <v>7140997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819402</v>
+        <v>119819409</v>
       </c>
       <c r="B11" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,26 +1704,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717018</v>
+        <v>716976</v>
       </c>
       <c r="R11" t="n">
-        <v>7141012</v>
+        <v>7141127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819406</v>
+        <v>119819402</v>
       </c>
       <c r="B13" t="n">
-        <v>89269</v>
+        <v>91874</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,30 +1922,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717000</v>
+        <v>717018</v>
       </c>
       <c r="R13" t="n">
-        <v>7140997</v>
+        <v>7141012</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819408</v>
+        <v>119819410</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716977</v>
+        <v>716975</v>
       </c>
       <c r="R14" t="n">
-        <v>7141124</v>
+        <v>7141125</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819415</v>
+        <v>119819399</v>
       </c>
       <c r="B15" t="n">
-        <v>89269</v>
+        <v>91874</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716957</v>
+        <v>716725</v>
       </c>
       <c r="R15" t="n">
-        <v>7141116</v>
+        <v>7140977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819405</v>
+        <v>119819416</v>
       </c>
       <c r="B17" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717053</v>
+        <v>716940</v>
       </c>
       <c r="R17" t="n">
-        <v>7141031</v>
+        <v>7141151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819409</v>
+        <v>119819408</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,21 +2481,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716976</v>
+        <v>716977</v>
       </c>
       <c r="R18" t="n">
-        <v>7141127</v>
+        <v>7141124</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819399</v>
+        <v>119819405</v>
       </c>
       <c r="B19" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716725</v>
+        <v>717053</v>
       </c>
       <c r="R19" t="n">
-        <v>7140977</v>
+        <v>7141031</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819400</v>
+        <v>119819398</v>
       </c>
       <c r="B20" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,30 +2699,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716743</v>
+        <v>716516</v>
       </c>
       <c r="R20" t="n">
-        <v>7140981</v>
+        <v>7141053</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819407</v>
+        <v>119819408</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716980</v>
+        <v>716977</v>
       </c>
       <c r="R6" t="n">
-        <v>7141022</v>
+        <v>7141124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819403</v>
+        <v>119819399</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
+        <v>91874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717069</v>
+        <v>716725</v>
       </c>
       <c r="R7" t="n">
-        <v>7141027</v>
+        <v>7140977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819400</v>
+        <v>119819398</v>
       </c>
       <c r="B8" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,30 +1367,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1399,13 +1399,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716743</v>
+        <v>716516</v>
       </c>
       <c r="R8" t="n">
-        <v>7140981</v>
+        <v>7141053</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819415</v>
+        <v>119819403</v>
       </c>
       <c r="B9" t="n">
         <v>89269</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716957</v>
+        <v>717069</v>
       </c>
       <c r="R9" t="n">
-        <v>7141116</v>
+        <v>7141027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819406</v>
+        <v>119819413</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,30 +1589,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717000</v>
+        <v>716959</v>
       </c>
       <c r="R10" t="n">
-        <v>7140997</v>
+        <v>7141129</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819409</v>
+        <v>119819415</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716976</v>
+        <v>716957</v>
       </c>
       <c r="R11" t="n">
-        <v>7141127</v>
+        <v>7141116</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819412</v>
+        <v>119819400</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,30 +1811,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716959</v>
+        <v>716743</v>
       </c>
       <c r="R12" t="n">
-        <v>7141129</v>
+        <v>7140981</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819402</v>
+        <v>119819401</v>
       </c>
       <c r="B13" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,30 +1922,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717018</v>
+        <v>716978</v>
       </c>
       <c r="R13" t="n">
-        <v>7141012</v>
+        <v>7140954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819410</v>
+        <v>119819416</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716975</v>
+        <v>716940</v>
       </c>
       <c r="R14" t="n">
-        <v>7141125</v>
+        <v>7141151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819399</v>
+        <v>119819407</v>
       </c>
       <c r="B15" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716725</v>
+        <v>716980</v>
       </c>
       <c r="R15" t="n">
-        <v>7140977</v>
+        <v>7141022</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819401</v>
+        <v>119819405</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716978</v>
+        <v>717053</v>
       </c>
       <c r="R16" t="n">
-        <v>7140954</v>
+        <v>7141031</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819416</v>
+        <v>119819410</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2366,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716940</v>
+        <v>716975</v>
       </c>
       <c r="R17" t="n">
-        <v>7141151</v>
+        <v>7141125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819408</v>
+        <v>119819406</v>
       </c>
       <c r="B18" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,30 +2477,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716977</v>
+        <v>717000</v>
       </c>
       <c r="R18" t="n">
-        <v>7141124</v>
+        <v>7140997</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819405</v>
+        <v>119819409</v>
       </c>
       <c r="B19" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717053</v>
+        <v>716976</v>
       </c>
       <c r="R19" t="n">
-        <v>7141031</v>
+        <v>7141127</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819398</v>
+        <v>119819402</v>
       </c>
       <c r="B20" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,26 +2703,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716516</v>
+        <v>717018</v>
       </c>
       <c r="R20" t="n">
-        <v>7141053</v>
+        <v>7141012</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112606190</v>
+        <v>119819408</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1038,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Avanäs, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716751</v>
+        <v>716977</v>
       </c>
       <c r="R5" t="n">
-        <v>7140964</v>
+        <v>7141124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,17 +1100,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819408</v>
+        <v>119819399</v>
       </c>
       <c r="B6" t="n">
         <v>91874</v>
@@ -1177,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716977</v>
+        <v>716725</v>
       </c>
       <c r="R6" t="n">
-        <v>7141124</v>
+        <v>7140977</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819399</v>
+        <v>119819398</v>
       </c>
       <c r="B7" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716725</v>
+        <v>716516</v>
       </c>
       <c r="R7" t="n">
-        <v>7140977</v>
+        <v>7141053</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819398</v>
+        <v>119819403</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1399,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716516</v>
+        <v>717069</v>
       </c>
       <c r="R8" t="n">
-        <v>7141053</v>
+        <v>7141027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819403</v>
+        <v>119819413</v>
       </c>
       <c r="B9" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,25 +1482,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717069</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>7141027</v>
+        <v>7141129</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819413</v>
+        <v>119819415</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1621,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716959</v>
+        <v>716957</v>
       </c>
       <c r="R10" t="n">
-        <v>7141129</v>
+        <v>7141116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819415</v>
+        <v>119819400</v>
       </c>
       <c r="B11" t="n">
         <v>89269</v>
@@ -1723,7 +1727,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,13 +1736,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716957</v>
+        <v>716743</v>
       </c>
       <c r="R11" t="n">
-        <v>7141116</v>
+        <v>7140981</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819400</v>
+        <v>119819401</v>
       </c>
       <c r="B12" t="n">
-        <v>89269</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,30 +1815,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1843,13 +1847,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716743</v>
+        <v>716978</v>
       </c>
       <c r="R12" t="n">
-        <v>7140981</v>
+        <v>7140954</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819401</v>
+        <v>119819416</v>
       </c>
       <c r="B13" t="n">
         <v>91858</v>
@@ -1954,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716978</v>
+        <v>716940</v>
       </c>
       <c r="R13" t="n">
-        <v>7140954</v>
+        <v>7141151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819416</v>
+        <v>119819407</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2033,25 +2037,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2065,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716940</v>
+        <v>716980</v>
       </c>
       <c r="R14" t="n">
-        <v>7141151</v>
+        <v>7141022</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819407</v>
+        <v>119819405</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2176,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716980</v>
+        <v>717053</v>
       </c>
       <c r="R15" t="n">
-        <v>7141022</v>
+        <v>7141031</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819405</v>
+        <v>119819410</v>
       </c>
       <c r="B16" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2287,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717053</v>
+        <v>716975</v>
       </c>
       <c r="R16" t="n">
-        <v>7141031</v>
+        <v>7141125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819410</v>
+        <v>119819406</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,30 +2370,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716975</v>
+        <v>717000</v>
       </c>
       <c r="R17" t="n">
-        <v>7141125</v>
+        <v>7140997</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819406</v>
+        <v>119819409</v>
       </c>
       <c r="B18" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,30 +2481,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2509,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717000</v>
+        <v>716976</v>
       </c>
       <c r="R18" t="n">
-        <v>7140997</v>
+        <v>7141127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819409</v>
+        <v>119819402</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,26 +2596,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2620,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716976</v>
+        <v>717018</v>
       </c>
       <c r="R19" t="n">
-        <v>7141127</v>
+        <v>7141012</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,117 +2688,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>119819402</v>
-      </c>
-      <c r="B20" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Avanäs, Vb</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>717018</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7141012</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103410738</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716438.0152394886</v>
+        <v>716438</v>
       </c>
       <c r="R2" t="n">
-        <v>7141106.915845793</v>
+        <v>7141107</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -748,19 +743,9 @@
           <t>2022-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,53 +777,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103410955</v>
+        <v>119819399</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Avanäs, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716948.6691792423</v>
+        <v>716725</v>
       </c>
       <c r="R3" t="n">
-        <v>7140981.622045009</v>
+        <v>7140977</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,50 +883,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159460</v>
+        <v>119819402</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Avanäs, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716750.8366396911</v>
+        <v>717018</v>
       </c>
       <c r="R4" t="n">
-        <v>7140964.144701021</v>
+        <v>7141012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,27 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,16 +992,11 @@
         <v>119819408</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1137,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819399</v>
+        <v>119819398</v>
       </c>
       <c r="B6" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1181,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716725</v>
+        <v>716516</v>
       </c>
       <c r="R6" t="n">
-        <v>7140977</v>
+        <v>7141053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,15 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819398</v>
+        <v>119819409</v>
       </c>
       <c r="B7" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716516</v>
+        <v>716976</v>
       </c>
       <c r="R7" t="n">
-        <v>7141053</v>
+        <v>7141127</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,37 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119819403</v>
+        <v>119819412</v>
       </c>
       <c r="B8" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1403,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717069</v>
+        <v>716959</v>
       </c>
       <c r="R8" t="n">
-        <v>7141027</v>
+        <v>7141129</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,15 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819413</v>
+        <v>119819407</v>
       </c>
       <c r="B9" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1514,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716959</v>
+        <v>716980</v>
       </c>
       <c r="R9" t="n">
-        <v>7141129</v>
+        <v>7141022</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,37 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819415</v>
+        <v>119819410</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1625,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716957</v>
+        <v>716975</v>
       </c>
       <c r="R10" t="n">
-        <v>7141116</v>
+        <v>7141125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,42 +1625,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819400</v>
+        <v>121150639</v>
       </c>
       <c r="B11" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1736,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716743</v>
+        <v>716722</v>
       </c>
       <c r="R11" t="n">
-        <v>7140981</v>
+        <v>7140990</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1803,19 +1731,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819401</v>
+        <v>103410955</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1836,24 +1759,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Avanäs, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716978</v>
+        <v>716949</v>
       </c>
       <c r="R12" t="n">
-        <v>7140954</v>
+        <v>7140981</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,17 +1796,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,19 +1833,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819416</v>
+        <v>112606190</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1947,21 +1861,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Avanäs, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716940</v>
+        <v>716751</v>
       </c>
       <c r="R13" t="n">
-        <v>7141151</v>
+        <v>7140964</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,17 +1898,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,15 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819407</v>
+        <v>119819401</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,21 +1946,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2069,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716980</v>
+        <v>716978</v>
       </c>
       <c r="R14" t="n">
-        <v>7141022</v>
+        <v>7140954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,15 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819405</v>
+        <v>119819416</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2180,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717053</v>
+        <v>716940</v>
       </c>
       <c r="R15" t="n">
-        <v>7141031</v>
+        <v>7141151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,15 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819410</v>
+        <v>129083700</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,41 +2158,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Avanäs, Vb</t>
+          <t>Finnbäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716975</v>
+        <v>716778</v>
       </c>
       <c r="R16" t="n">
-        <v>7141125</v>
+        <v>7141271</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,17 +2212,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,27 +2242,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819406</v>
+        <v>119819400</v>
       </c>
       <c r="B17" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,13 +2293,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717000</v>
+        <v>716743</v>
       </c>
       <c r="R17" t="n">
-        <v>7140997</v>
+        <v>7140981</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2469,37 +2360,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819409</v>
+        <v>119819403</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2513,10 +2399,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716976</v>
+        <v>717069</v>
       </c>
       <c r="R18" t="n">
-        <v>7141127</v>
+        <v>7141027</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,42 +2466,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819402</v>
+        <v>119819404</v>
       </c>
       <c r="B19" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2624,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717018</v>
+        <v>717069</v>
       </c>
       <c r="R19" t="n">
-        <v>7141012</v>
+        <v>7141039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,6 +2569,431 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119819406</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Avanäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>717000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7140997</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119819411</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Avanäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>716969</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7141143</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119819415</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Avanäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>716957</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7141116</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129083701</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Finnbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>716784</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7141240</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52101-2021 artfynd.xlsx
+++ b/artfynd/A 52101-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103410738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819399</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819402</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819408</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819398</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819409</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819412</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819407</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,6 +1778,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150639</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103410955</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606190</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2038,6 +2103,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819401</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819416</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129083700</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2357,6 +2437,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819400</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2463,6 +2548,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819403</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,6 +2659,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819404</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2675,6 +2770,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819406</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2781,6 +2881,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819411</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,6 +2992,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819415</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2994,8 +3104,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129083701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>